--- a/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
@@ -79,12 +79,12 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>JALAPA</t>
   </si>
   <si>
@@ -100,12 +100,12 @@
     <t>ROCETE</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>LUGO</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -121,10 +121,10 @@
     <t>ALEXIS</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
     <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>AZUL ARIADNA</t>
   </si>
   <si>
     <t>JAZMIN</t>
@@ -966,7 +966,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920340</v>
+        <v>22330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920353</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1004,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -76,67 +76,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>JALAPA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>ROCETE</t>
   </si>
   <si>
-    <t>LUGO</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
   </si>
   <si>
     <t>ALEXIS</t>
   </si>
   <si>
-    <t>ZAYRA</t>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
     <t>AZUL ARIADNA</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
   </si>
 </sst>
 </file>
@@ -911,7 +920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -943,16 +952,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920321</v>
+        <v>22330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -966,16 +975,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920100</v>
+        <v>22330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -989,22 +998,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920353</v>
+        <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1012,45 +1021,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920339</v>
+        <v>22330051920212</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920333</v>
+        <v>22330051920321</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1058,22 +1067,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920212</v>
+        <v>22330051920339</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1087,10 +1096,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1099,6 +1108,29 @@
         <v>12</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920353</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -128,9 +122,6 @@
   </si>
   <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
@@ -920,7 +911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,10 +949,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -981,10 +972,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -998,22 +989,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920212</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1021,45 +1012,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920212</v>
+        <v>22330051920321</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920321</v>
+        <v>22330051920339</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1067,22 +1058,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920339</v>
+        <v>22330051920130</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1090,16 +1081,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920130</v>
+        <v>22330051920353</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1108,29 +1099,6 @@
         <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920353</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -82,15 +82,45 @@
     <t>LARRACILLA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>JALAPA</t>
   </si>
   <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -103,15 +133,39 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
     <t>ROCETE</t>
   </si>
   <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>OJEDA</t>
   </si>
   <si>
@@ -124,13 +178,43 @@
     <t>MONSERRAT</t>
   </si>
   <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
     <t>ALEXIS</t>
   </si>
   <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
     <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>AHILY</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>ABIGAIL ANTONIA</t>
@@ -680,16 +764,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>79.41</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -703,16 +790,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -726,16 +816,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -749,16 +842,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H5">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -814,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>88.23999999999999</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -840,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>86.05</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -866,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>87.5</v>
+        <v>70</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -892,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>78.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,10 +1045,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -972,10 +1068,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -989,16 +1085,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1012,85 +1108,85 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920321</v>
+        <v>22330051920212</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920339</v>
+        <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920130</v>
+        <v>22330051920071</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920353</v>
+        <v>22330051920354</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1099,6 +1195,236 @@
         <v>12</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920321</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920382</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920339</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920054</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920064</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920334</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920353</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
@@ -842,7 +842,7 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>12</v>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -79,33 +79,36 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
     <t>OLMOS</t>
   </si>
   <si>
@@ -130,33 +133,36 @@
     <t>QUERO</t>
   </si>
   <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>GIL</t>
   </si>
   <si>
@@ -175,33 +181,39 @@
     <t>DIEGO JESUS</t>
   </si>
   <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
     <t>MONSERRAT</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
     <t>AHILY</t>
   </si>
   <si>
@@ -212,9 +224,6 @@
   </si>
   <si>
     <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
   <si>
     <t>ABIGAIL ANTONIA</t>
@@ -1007,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1045,10 +1054,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1062,22 +1071,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920340</v>
+        <v>22330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1085,22 +1094,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920061</v>
+        <v>22330051920105</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1108,7 +1117,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -1117,7 +1126,7 @@
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1131,7 +1140,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920068</v>
+        <v>22330051920212</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1140,7 +1149,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1154,7 +1163,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920071</v>
+        <v>22330051920068</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1163,7 +1172,7 @@
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1177,22 +1186,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920354</v>
+        <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1200,39 +1209,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920321</v>
+        <v>22330051920354</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920382</v>
+        <v>22330051920010</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1246,22 +1255,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920339</v>
+        <v>22330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1269,16 +1278,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920107</v>
+        <v>22330051920339</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1292,16 +1301,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920122</v>
+        <v>22330051920340</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1315,22 +1324,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920054</v>
+        <v>22330051920107</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1338,22 +1347,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920064</v>
+        <v>22330051920122</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1361,16 +1370,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920334</v>
+        <v>22330051920054</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1384,22 +1393,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920130</v>
+        <v>22330051920064</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1407,24 +1416,70 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
+        <v>22330051920334</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920130</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
         <v>22330051920353</v>
       </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="G18">
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="97">
   <si>
     <t>Mat</t>
   </si>
@@ -76,160 +76,238 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JORGE</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
+    <t>TENORIO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>QUERO</t>
   </si>
   <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
     <t>ZARATE</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CHIMALHUA</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
+    <t>SILVA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>OJEDA</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
     <t>OSMAR UZIEL</t>
   </si>
   <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>VALENTINA</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER ANDRUS</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>DANIELA</t>
+    <t>AHILY</t>
+  </si>
+  <si>
+    <t>SALMA AISHA</t>
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>AHILY</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
     <t>DANIEL ELEAZAR</t>
   </si>
   <si>
+    <t>HANNY YUSETH</t>
+  </si>
+  <si>
+    <t>ROSA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
     <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
+  </si>
+  <si>
     <t>AZUL ARIADNA</t>
+  </si>
+  <si>
+    <t>ORESTES</t>
   </si>
 </sst>
 </file>
@@ -919,16 +997,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>79.41</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -954,7 +1032,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -971,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -997,16 +1075,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>71.43000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1016,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1048,16 +1126,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920015</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1071,16 +1149,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920382</v>
+        <v>22330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1094,22 +1172,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920105</v>
+        <v>22330051920018</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1117,22 +1195,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920061</v>
+        <v>22330051920321</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1140,22 +1218,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920212</v>
+        <v>22330051920382</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1163,16 +1241,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920068</v>
+        <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1186,16 +1264,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920071</v>
+        <v>22330051920061</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1209,22 +1287,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920354</v>
+        <v>22330051920071</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1232,16 +1310,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920010</v>
+        <v>22330051920013</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1255,16 +1333,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920321</v>
+        <v>22330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1278,22 +1356,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920339</v>
+        <v>22330051920332</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1301,16 +1379,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920340</v>
+        <v>22330051920098</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1324,16 +1402,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920107</v>
+        <v>22330051920339</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1347,16 +1425,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920122</v>
+        <v>22330051920340</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1370,22 +1448,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920054</v>
+        <v>22330051920105</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1393,22 +1471,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920064</v>
+        <v>22330051920107</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1416,16 +1494,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920334</v>
+        <v>22330051920058</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1439,22 +1517,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920130</v>
+        <v>22330051920062</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1462,24 +1540,300 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
+        <v>22330051920212</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920064</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920334</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22230030070114</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920070</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920317</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920079</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920343</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920130</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920133</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920138</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
         <v>22330051920353</v>
       </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
         <v>12</v>
       </c>
-      <c r="G20">
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>22330051920143</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32">
         <v>1</v>
       </c>
     </row>
